--- a/docs/chapter4_final/08_chapter/chapter_tables.xlsx
+++ b/docs/chapter4_final/08_chapter/chapter_tables.xlsx
@@ -26,6 +26,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 4.17" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 4.18" sheetId="18" state="visible" r:id="rId18"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 4.19" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 4.20" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 4.21" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 4.22" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -871,164 +874,587 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table 4.11: Description of the replicate 1 dataset</t>
+          <t>Table 4.11: Fictional customer companies used in the simulation</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Measure</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Contact person</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>E-mail</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Orders</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Orders</t>
+          <t>Adeyemi &amp; Sons Construction Ltd</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>Folake Adeyemi</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>folake.adeyemi@adeyemi1.example</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Ikeja</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Clean, rule-targeted and no-rule orders</t>
+          <t>Agege Steel Works</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>200, 240, 60</t>
+          <t>Yusuf Adebanjo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>yusuf.adebanjo@agege13.example</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Ikeja</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Ajah Sunrise Housing Co-op</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>Blessing Okoro</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>blessing.okoro@ajah14.example</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Lekki-Ajah</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Orders per customer</t>
+          <t>Apapa Port Works Supplies</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16 to 42</t>
+          <t>Garba Usman</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>garba.usman@apapa20.example</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Lagos Mainland</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mean lines per order</t>
+          <t>Bodija Interiors</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>Segun Olatunji</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>segun.olatunji@bodija16.example</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Ibadan</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mean units per order</t>
+          <t>Eko Bridge Contractors</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>Tolulope Ogunleye</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>tolulope.ogunleye@eko6.example</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Lagos Island</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>36</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Order value, mean</t>
+          <t>Greenfield Estates Nigeria</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₦1,594,495.04</t>
+          <t>Ngozi Eze</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ngozi.eze@greenfield7.example</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Lekki-Ajah</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Order value, median</t>
+          <t>Gwarinpa Homes Ltd</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₦981,367.50</t>
+          <t>Fatima Sani</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>fatima.sani@gwarinpa15.example</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Order value, range</t>
+          <t>Ibadan Prime Homes Ltd</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₦8,815.00 to ₦20,725,462.50</t>
+          <t>Oluwaseun Afolabi</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>oluwaseun.afolabi@ibadan3.example</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Ibadan</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total order value</t>
+          <t>Kanu Brothers Building Supplies</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₦797,247,520.00</t>
+          <t>Chukwuemeka Kanu</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>chukwuemeka.kanu@kanu2.example</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Lagos Mainland</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Orders by region</t>
+          <t>Lekki Coastal Developers</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lagos Mainland 102; Ibadan 93; Ikeja 80; Lagos Island 76; Lekki-Ajah 74; Abuja 55; No address given 20</t>
+          <t>Amina Bello</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>amina.bello@lekki4.example</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Lekki-Ajah</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Source: replicate 1, database run 5, 07_analysis/metrics_final.json dataset.</t>
+          <t>Magodo Residential Ltd</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Funmilayo Adeleke</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>funmilayo.adeleke@magodo19.example</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Ikeja</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Marina Point Facilities</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kemi Lawson</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>kemi.lawson@marina11.example</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Lagos Island</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Northgate Realty Abuja</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ibrahim Musa</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ibrahim.musa@northgate5.example</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ola-Ade Hardware &amp; Tiles</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Babatunde Oladipo</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>babatunde.oladipo@olaade8.example</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Ikeja</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Oyo Central Builders</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Adewale Akinyemi</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>adewale.akinyemi@oyo10.example</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Ibadan</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Surulere Paint &amp; Finish</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Uche Nwosu</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>uche.nwosu@surulere12.example</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Lagos Mainland</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Victoria Island Fit-Out Ltd</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Chiamaka Obi</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>chiamaka.obi@victoria17.example</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Lagos Island</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Yaba Tech Hub Builders</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Emeka Okafor</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>emeka.okafor@yaba18.example</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Lagos Mainland</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Zuma Rock Engineering</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Hauwa Abdullahi</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>hauwa.abdullahi@zuma9.example</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Source: replicate 1, database run 5, 03_simulation/replicate1_orders.csv. All names and contact details are fictional.</t>
         </is>
       </c>
     </row>
@@ -1043,131 +1469,59 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table 4.12: Detection by planted error type, replicate 1</t>
+          <t>Table 4.12: Description of the replicate 1 dataset</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Planted error</t>
+          <t>Measure</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Has rule</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Flagged</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Detection %</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>95% CI</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Caught by expected rule</t>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Clean order (no error)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>28 flagged</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>14.0 false alarms</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>9.9 to 19.5</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>Orders</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SKU not in catalogue</t>
+          <t>Clean, rule-targeted and no-rule orders</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>20/20</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>83.9 to 100.0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>200, 240, 60</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Discontinued product</t>
+          <t>Customers</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>20/20</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>83.9 to 100.0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -1176,423 +1530,103 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Missing delivery address</t>
+          <t>Orders per customer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>20/20</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>83.9 to 100.0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>16 to 42</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Missing delivery date</t>
+          <t>Mean lines per order</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>20/20</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>83.9 to 100.0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>2.31</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Delivery date in the past</t>
+          <t>Mean units per order</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>20/20</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>83.9 to 100.0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>126.5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Quantity below minimum</t>
+          <t>Order value, mean</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>20/20</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>83.9 to 100.0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>₦1,594,495.04</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Quantity above maximum</t>
+          <t>Order value, median</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>20/20</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>83.9 to 100.0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>₦981,367.50</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Fractional quantity</t>
+          <t>Order value, range</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>20/20</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>83.9 to 100.0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>₦8,815.00 to ₦20,725,462.50</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Quantity above available stock</t>
+          <t>Total order value</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>20/20</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>83.9 to 100.0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>₦797,247,520.00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Duplicate order</t>
+          <t>Orders by region</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>20/20</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>83.9 to 100.0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>Lagos Mainland 102; Ibadan 93; Ikeja 80; Lagos Island 76; Lekki-Ajah 74; Abuja 55; No address given 20</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Customer account not active</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>20/20</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>83.9 to 100.0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Price changed after the order was saved</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>20/20</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>83.9 to 100.0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Wrong but valid product</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>5/20</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>11.2 to 46.9</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>5 by other rules</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Plausible quantity typing slip</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>14/20</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>48.1 to 85.5</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>14 by other rules</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Wrong saved address</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>5/20</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>11.2 to 46.9</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>5 by other rules</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Source: replicate 1, 07_analysis/metrics_final.json by_type, workbook sheet R1 Summary section D.</t>
+          <t>Source: replicate 1, database run 5, 07_analysis/metrics_final.json dataset.</t>
         </is>
       </c>
     </row>
@@ -1607,116 +1641,564 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table 4.13: Confusion matrices, replicate 1</t>
+          <t>Table 4.13: Sample of simulated orders and the decision taken, replicate 1</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Measure set</t>
+          <t>Order</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Error flagged</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Error passed</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Clean flagged</t>
+          <t>Planted error</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Clean passed</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orders</t>
+          <t>First message shown</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Primary, all errors</t>
+          <t>ORD-3788</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>Bodija Interiors</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>₦418,175.00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>Clean order (no error)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Secondary, rule-targeted errors</t>
+          <t>ORD-3800</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>Marina Point Facilities</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>₦869,030.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>SKU not in catalogue</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>Row 4: XX-680 - not in the catalogue</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Source: replicate 1, 07_analysis/metrics_final.json confusion_all_errors and confusion_rule_targeted, workbook R1 Summary sections B and C.</t>
+          <t>ORD-3784</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Marina Point Facilities</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>₦1,656,575.00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Discontinued product</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SAND-T is no longer sold. Remove it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ORD-3782</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Bodija Interiors</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>₦559,000.00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Missing delivery address</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Choose a delivery address.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ORD-3783</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Gwarinpa Homes Ltd</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>₦1,078,225.00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Missing delivery date</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Choose a delivery date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ORD-3789</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Marina Point Facilities</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>₦522,665.00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Delivery date in the past</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>The delivery date is in the past.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ORD-3805</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Magodo Residential Ltd</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>₦621,995.00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Quantity below minimum</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>PVC pipe, 2 inch, 6 m: quantity must be between 2 and 500.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ORD-3793</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Lekki Coastal Developers</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>₦15,103,642.50</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Quantity above maximum</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Aluminium roofing sheet, 0.55 mm: quantity must be between 10 and 1000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ORD-3785</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Victoria Island Fit-Out Ltd</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>₦732,075.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Fractional quantity</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>PVC-4 - Quantity must be a whole number</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ORD-3786</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Bodija Interiors</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>₦6,077,405.00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Quantity above available stock</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Iron rod, 12 mm: not enough stock for this quantity. Reduce it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ORD-3838</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Victoria Island Fit-Out Ltd</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>₦764,970.00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Duplicate order</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Warned</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Iron rod, 12 mm: 97 is far above this customer's usual 29.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ORD-3798</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Gwarinpa Homes Ltd</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>₦24,940.00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Customer account not active</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>The customer account is not active.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ORD-3802</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Oyo Central Builders</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>₦234,350.00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Price changed after the order was saved</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Cement, 50 kg bag: price changed from 9500.00 to 10000.00. Save the order again to update it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ORD-3806</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Gwarinpa Homes Ltd</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>₦1,030,925.00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Wrong but valid product</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ORD-3792</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ajah Sunrise Housing Co-op</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>₦3,445,805.00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Plausible quantity typing slip</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Warned</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Cement, 50 kg bag: 190 is far above this customer's usual 23.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ORD-3812</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ola-Ade Hardware &amp; Tiles</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>₦859,677.50</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Wrong saved address</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Source: replicate 1, database run 5, first order of each kind in 03_simulation/replicate1_orders.csv.</t>
         </is>
       </c>
     </row>
@@ -1731,111 +2213,118 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table 4.14: Validation measures with 95 percent Wilson intervals, replicate 1</t>
+          <t>Table 4.14: Detection by planted error type, replicate 1</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Measure</t>
+          <t>Planted error</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Primary %</t>
+          <t>Has rule</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Primary 95% CI</t>
+          <t>Flagged</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Secondary %</t>
+          <t>Detection %</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Secondary 95% CI</t>
+          <t>95% CI</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Caught by expected rule</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Accuracy</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>87.2</t>
-        </is>
-      </c>
+          <t>Clean order (no error)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>84.0 to 89.8</t>
+          <t>28 flagged</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>14.0 false alarms</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>91.0 to 95.6</t>
-        </is>
-      </c>
+          <t>9.9 to 19.5</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Precision</t>
+          <t>SKU not in catalogue</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>86.5 to 93.3</t>
+          <t>20/20</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>85.3 to 92.7</t>
+          <t>83.9 to 100.0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Discontinued product</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>83.8 to 91.2</t>
+          <t>20/20</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1845,95 +2334,435 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>98.4 to 100.0</t>
+          <t>83.9 to 100.0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Specificity</t>
+          <t>Missing delivery address</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>80.5 to 90.1</t>
+          <t>20/20</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>80.5 to 90.1</t>
+          <t>83.9 to 100.0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>False-alarm rate</t>
+          <t>Missing delivery date</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>9.9 to 19.5</t>
+          <t>20/20</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>9.9 to 19.5</t>
+          <t>83.9 to 100.0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F1 score</t>
+          <t>Delivery date in the past</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>not a single proportion</t>
+          <t>20/20</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>not a single proportion</t>
+          <t>83.9 to 100.0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Source: replicate 1, 07_analysis/metrics_final.json, workbook R1 Summary sections B and C.</t>
+          <t>Quantity below minimum</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>20/20</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>83.9 to 100.0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Quantity above maximum</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>20/20</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>83.9 to 100.0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Fractional quantity</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>20/20</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>83.9 to 100.0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Quantity above available stock</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>20/20</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>83.9 to 100.0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Duplicate order</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>20/20</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>83.9 to 100.0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Customer account not active</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>20/20</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>83.9 to 100.0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Price changed after the order was saved</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>20/20</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>83.9 to 100.0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Wrong but valid product</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>5/20</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>11.2 to 46.9</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>5 by other rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Plausible quantity typing slip</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>14/20</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>48.1 to 85.5</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>14 by other rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Wrong saved address</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>5/20</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>11.2 to 46.9</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>5 by other rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Source: replicate 1, 07_analysis/metrics_final.json by_type, workbook sheet R1 Summary section D.</t>
         </is>
       </c>
     </row>
@@ -1948,390 +2777,139 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table 4.15: Rule activity and false alarms, replicate 1</t>
+          <t>Table 4.15: Definitions of the classification measures</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Rule</t>
+          <t>Measure</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Severity</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Orders fired</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>On its target type</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>On other error types</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>On clean orders</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>False alarms per clean order, 95% CI</t>
+          <t>Formula</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mandatory fields</t>
+          <t>Accuracy</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Blocking</t>
+          <t>Share of all orders the system judged correctly, erroneous orders flagged and clean orders passed</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0.0 (0.0 to 1.9)</t>
+          <t>(TP + TN) / all orders</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SKU and product active</t>
+          <t>Precision</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Blocking</t>
+          <t>Of the orders flagged, the share that really carried an error</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0.0 (0.0 to 1.9)</t>
+          <t>TP / (TP + FP)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Quantity limits</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Blocking</t>
+          <t>Of the orders that carried an error, the share the system flagged</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0.0 (0.0 to 1.9)</t>
+          <t>TP / (TP + FN)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Stock availability</t>
+          <t>Specificity</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Blocking</t>
+          <t>Of the clean orders, the share passed without a flag</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0.0 (0.0 to 1.9)</t>
+          <t>TN / (TN + FP)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Customer status</t>
+          <t>False-alarm rate</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Blocking</t>
+          <t>Of the clean orders, the share flagged</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0.0 (0.0 to 1.9)</t>
+          <t>FP / (FP + TN)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pricing</t>
+          <t>F1 score</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Blocking</t>
+          <t>Harmonic mean of precision and recall</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0.0 (0.0 to 1.9)</t>
+          <t>2 x P x R / (P + R)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Delivery date and address</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Blocking</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0.0 (0.0 to 1.9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Duplicate order</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0.5 (0.1 to 2.8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Unusual quantity</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>13.5 (9.4 to 18.9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Source: replicate 1, 07_analysis/metrics_final.json rules, workbook R1 Summary section E.</t>
+          <t>Source: standard definitions. TP true positive, FN false negative, FP false positive, TN true negative.</t>
         </is>
       </c>
     </row>
@@ -2346,236 +2924,116 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table 4.16: Validation time per order in milliseconds, replicate 1</t>
+          <t>Table 4.16: Confusion matrices, replicate 1</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Statistic</t>
+          <t>Measure set</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>All orders</t>
+          <t>Error flagged</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Error passed</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Warned</t>
+          <t>Clean flagged</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Clean passed</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Orders</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Orders</t>
+          <t>Primary, all errors</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>500</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>220</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mean</t>
+          <t>Secondary, rule-targeted errors</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>28.72</t>
+          <t>240</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>27.85</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>28</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>440</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SD, sample</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>23.27</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>21.34</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>25.28</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>24.33</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Median</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>22.16</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>22.31</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>22.59</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>21.56</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>95th percentile</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>74.72</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>71.59</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>80.19</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>75.57</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Minimum</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>4.81</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Maximum</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>124.31</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>94.84</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>114.3</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>124.31</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Source: replicate 1, 07_analysis/metrics_final.json validation_ms, workbook R1 Summary section F.</t>
+          <t>Source: replicate 1, 07_analysis/metrics_final.json confusion_all_errors and confusion_rule_targeted, workbook R1 Summary sections B and C.</t>
         </is>
       </c>
     </row>
@@ -2590,13 +3048,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table 4.17: Key measures in each replicate</t>
+          <t>Table 4.17: Validation measures with 95 percent Wilson intervals, replicate 1</t>
         </is>
       </c>
     </row>
@@ -2608,29 +3066,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Replicate 1</t>
+          <t>Primary %</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Replicate 2</t>
+          <t>Primary 95% CI</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Replicate 3</t>
+          <t>Secondary %</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Secondary 95% CI</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Accuracy, all errors</t>
+          <t>Accuracy</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2640,24 +3098,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>84.0 to 89.8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>86.8 to 87.2</t>
+          <t>91.0 to 95.6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Precision, all errors</t>
+          <t>Precision</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2667,24 +3125,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>86.5 to 93.3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>89.5 to 90.4</t>
+          <t>85.3 to 92.7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Recall, all errors</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2694,17 +3152,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>83.8 to 91.2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>88.0 to 88.3</t>
+          <t>98.4 to 100.0</t>
         </is>
       </c>
     </row>
@@ -2721,17 +3179,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>80.5 to 90.1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>84.5 to 86.0</t>
+          <t>80.5 to 90.1</t>
         </is>
       </c>
     </row>
@@ -2748,24 +3206,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>9.9 to 19.5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14.0 to 15.5</t>
+          <t>9.9 to 19.5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F1, all errors</t>
+          <t>F1 score</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2775,267 +3233,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>not a single proportion</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>88.9 to 89.2</t>
+          <t>not a single proportion</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Accuracy, rule-targeted errors</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>93.6</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>93.4</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>93.0 to 93.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Precision, rule-targeted errors</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>89.6</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>88.6</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>88.6 to 89.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Recall, rule-targeted errors</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>100.0 to 100.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>F1, rule-targeted errors</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>94.5</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>93.9</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>94.3</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>93.9 to 94.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>No-rule errors flagged</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>41.7</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>41.7</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>40.0 to 41.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Mean validation time, ms</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>28.72</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>29.84</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2.33</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2.33 to 29.84</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Median validation time, ms</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>22.16</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>22.88</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>2.34 to 22.88</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>95th percentile validation time, ms</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>74.72</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>78.92</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2.84</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>2.84 to 78.92</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Mandatory-field completion, orders reaching approval</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>100.0 to 100.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Source: 07_analysis/metrics_final.json replicate_range, workbook sheet Replicate range.</t>
+          <t>Source: replicate 1, 07_analysis/metrics_final.json, workbook R1 Summary sections B and C.</t>
         </is>
       </c>
     </row>
@@ -3050,349 +3265,390 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table 4.18: Unusual-quantity sensitivity on replicate 1</t>
+          <t>Table 4.18: Rule activity and false alarms, replicate 1</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Threshold</t>
+          <t>Rule</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Earlier orders</t>
+          <t>Severity</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Clean flagged</t>
+          <t>Orders fired</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>False-alarm %</t>
+          <t>On its target type</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>95% CI</t>
+          <t>On other error types</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slips flagged</t>
+          <t>On clean orders</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Slip detection %</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>95% CI</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Accuracy, all errors %</t>
+          <t>False alarms per clean order, 95% CI</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3 x average</t>
+          <t>Mandatory fields</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Blocking</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28/200</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9.9 to 19.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>14/20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>48.1 to 85.5</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>87.2</t>
+          <t>0.0 (0.0 to 1.9)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4 x average</t>
+          <t>SKU and product active</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Blocking</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20/200</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>6.6 to 14.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>12/20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>38.7 to 78.1</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>88.0</t>
+          <t>0.0 (0.0 to 1.9)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5 x average</t>
+          <t>Quantity limits</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Blocking</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>17/200</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5.4 to 13.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>11/20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>55.0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>34.2 to 74.2</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>88.2</t>
+          <t>0.0 (0.0 to 1.9)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3 x average</t>
+          <t>Stock availability</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Blocking</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38/200</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>14.2 to 25.0</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>16/20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>58.4 to 91.9</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>85.4</t>
+          <t>0.0 (0.0 to 1.9)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4 x average</t>
+          <t>Customer status</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Blocking</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>23/200</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>7.8 to 16.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14/20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>48.1 to 85.5</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>88.0</t>
+          <t>0.0 (0.0 to 1.9)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5 x average</t>
+          <t>Pricing</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Blocking</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16/200</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5.0 to 12.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>12/20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>38.7 to 78.1</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>88.6</t>
+          <t>0.0 (0.0 to 1.9)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Source: replays of database run 5 as runs 8 to 13, 04_sensitivity/sensitivity_results.csv, workbook sheet Sensitivity.</t>
+          <t>Delivery date and address</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Blocking</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.0 (0.0 to 1.9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Duplicate order</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.5 (0.1 to 2.8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Unusual quantity</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>13.5 (9.4 to 18.9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Source: replicate 1, 07_analysis/metrics_final.json rules, workbook R1 Summary section E.</t>
         </is>
       </c>
     </row>
@@ -3407,209 +3663,236 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table 4.19: Objectives and success criteria</t>
+          <t>Table 4.19: Validation time per order in milliseconds, replicate 1</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Objective</t>
+          <t>Statistic</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>All orders</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Result</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>95% CI</t>
+          <t>Warned</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[EXACT CHAPTER ONE WORDING NEEDED] Objective 2, validation engine for SKU, quantity, customer details, pricing, duplicate orders, stock and mandatory fields</t>
+          <t>Orders</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>At least 90 percent validation accuracy</t>
+          <t>500</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Primary 87.2 percent, all errors. Secondary 93.6 percent, rule-targeted errors. Replicates 86.8 to 87.2 and 93.0 to 93.6</t>
+          <t>208</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>84.0 to 89.8 and 91.0 to 95.6</t>
+          <t>72</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Partly met</t>
+          <t>220</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[EXACT CHAPTER ONE WORDING NEEDED] Objective 3, fewer manual entry errors</t>
+          <t>Mean</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>At least 60 percent fewer manual entry errors</t>
+          <t>28.72</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[DATA PENDING]</t>
+          <t>27.85</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[DATA PENDING]</t>
+          <t>31.84</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>28.53</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[EXACT CHAPTER ONE WORDING NEEDED] Objective 3, mandatory fields</t>
+          <t>SD, sample</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100 percent mandatory-field completion</t>
+          <t>23.27</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>258 of 258 orders reaching approval, 100 percent in all three replicates</t>
+          <t>21.34</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>98.5 to 100.0</t>
+          <t>25.28</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Met</t>
+          <t>24.33</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[EXACT CHAPTER ONE WORDING NEEDED] Objective 4, processing speed</t>
+          <t>Median</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>30 to 50 percent faster processing</t>
+          <t>22.16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[DATA PENDING]</t>
+          <t>22.31</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[DATA PENDING]</t>
+          <t>22.59</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>21.56</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[EXACT CHAPTER ONE WORDING NEEDED] Objective 5, usability and acceptance</t>
+          <t>95th percentile</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Usability and acceptance shown by the questionnaire</t>
+          <t>74.72</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[DATA PENDING]</t>
+          <t>71.59</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[DATA PENDING]</t>
+          <t>80.19</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>75.57</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[EXACT CHAPTER ONE WORDING NEEDED] Objective 5, simulated orders</t>
+          <t>Minimum</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>500 simulated orders processed</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>500 orders in each of three replicates, 1,500 in all</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>not applicable</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Met</t>
+          <t>2.45</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Source: Sections 4.2 to 4.5. Accuracy judged on the primary measure with the secondary measure in support.</t>
+          <t>Maximum</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>124.31</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>94.84</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>114.3</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>124.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Source: replicate 1, 07_analysis/metrics_final.json validation_ms, workbook R1 Summary section F.</t>
         </is>
       </c>
     </row>
@@ -3731,6 +4014,1040 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Table 4.20: Key measures in each replicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Measure</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Replicate 1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Replicate 2</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Replicate 3</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Range</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Accuracy, all errors</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>87.2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>86.8</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>87.2</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>86.8 to 87.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Precision, all errors</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>90.4</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>90.1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>89.5 to 90.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Recall, all errors</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>88.3</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>88.3</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>88.0 to 88.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Specificity</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>84.5 to 86.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>False-alarm rate</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>15.5</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>14.5</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>14.0 to 15.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F1, all errors</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>88.9</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>88.9 to 89.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Accuracy, rule-targeted errors</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>93.6</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>93.4</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>93.0 to 93.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Precision, rule-targeted errors</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>89.6</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>88.6</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>88.6 to 89.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Recall, rule-targeted errors</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>100.0 to 100.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F1, rule-targeted errors</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>94.5</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>93.9</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>94.3</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>93.9 to 94.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>No-rule errors flagged</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>41.7</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>41.7</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>40.0 to 41.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Mean validation time, ms</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>28.72</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>29.84</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2.33 to 29.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Median validation time, ms</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>22.16</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>22.88</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2.34 to 22.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>95th percentile validation time, ms</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>74.72</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>78.92</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2.84</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2.84 to 78.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Mandatory-field completion, orders reaching approval</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>100.0 to 100.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Source: 07_analysis/metrics_final.json replicate_range, workbook sheet Replicate range.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Table 4.21: Unusual-quantity sensitivity on replicate 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Threshold</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Earlier orders</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Clean flagged</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>False-alarm %</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>95% CI</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Slips flagged</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Slip detection %</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>95% CI</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Accuracy, all errors %</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>3 x average</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>28/200</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>9.9 to 19.5</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>14/20</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>48.1 to 85.5</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>87.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>4 x average</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>20/200</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>6.6 to 14.9</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>12/20</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>38.7 to 78.1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>5 x average</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>17/200</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>5.4 to 13.2</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>11/20</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>34.2 to 74.2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>88.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3 x average</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>38/200</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>14.2 to 25.0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>16/20</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>58.4 to 91.9</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>85.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4 x average</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>23/200</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>7.8 to 16.7</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>14/20</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>48.1 to 85.5</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>5 x average</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>16/200</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5.0 to 12.6</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>12/20</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>38.7 to 78.1</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>88.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Source: replays of database run 5 as runs 8 to 13, 04_sensitivity/sensitivity_results.csv, workbook sheet Sensitivity.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Table 4.22: Objectives and success criteria</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Objective</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Criterion</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>95% CI</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>[EXACT CHAPTER ONE WORDING NEEDED] Objective 2, validation engine for SKU, quantity, customer details, pricing, duplicate orders, stock and mandatory fields</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>At least 90 percent validation accuracy</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Primary 87.2 percent, all errors. Secondary 93.6 percent, rule-targeted errors. Replicates 86.8 to 87.2 and 93.0 to 93.6</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>84.0 to 89.8 and 91.0 to 95.6</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Partly met</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>[EXACT CHAPTER ONE WORDING NEEDED] Objective 3, fewer manual entry errors</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>At least 60 percent fewer manual entry errors</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[DATA PENDING]</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>[DATA PENDING]</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>[EXACT CHAPTER ONE WORDING NEEDED] Objective 3, mandatory fields</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>100 percent mandatory-field completion</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>258 of 258 orders reaching approval, 100 percent in all three replicates</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>98.5 to 100.0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Met</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>[EXACT CHAPTER ONE WORDING NEEDED] Objective 4, processing speed</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>30 to 50 percent faster processing</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[DATA PENDING]</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>[DATA PENDING]</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>[EXACT CHAPTER ONE WORDING NEEDED] Objective 5, usability and acceptance</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Usability and acceptance shown by the questionnaire</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[DATA PENDING]</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>[DATA PENDING]</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>[EXACT CHAPTER ONE WORDING NEEDED] Objective 5, simulated orders</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>500 simulated orders processed</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>500 orders in each of three replicates, 1,500 in all</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>not applicable</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Met</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Source: Sections 4.2 to 4.5. Accuracy judged on the primary measure with the secondary measure in support.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/docs/chapter4_final/08_chapter/chapter_tables.xlsx
+++ b/docs/chapter4_final/08_chapter/chapter_tables.xlsx
@@ -3069,20 +3069,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table 4.18: Objectives and success criteria</t>
+          <t>Table 4.18: Objectives of Section 1.3 and their success criteria</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Objective</t>
+          <t>Objective, Chapter One wording</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3109,142 +3109,196 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[EXACT CHAPTER ONE WORDING NEEDED] Objective 2, validation engine for SKU, quantity, customer details, pricing, duplicate orders, stock and mandatory fields</t>
+          <t>1. To design and develop a web-based order processing system that replaces manual order entry done through Excel sheets and through e-mail and WhatsApp messages.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>At least 90 percent validation accuracy</t>
+          <t>A working web-based system through which orders are entered and processed without rekeying</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Primary 87.2 percent, all errors. Secondary 93.6 percent, rule-targeted errors. Replicates 86.8 to 87.2 and 93.0 to 93.6</t>
+          <t>Built and deployed. Orders are entered in the portal, from an uploaded Excel or CSV sheet, or from a pasted message. 23 of 26 functional tests passed. CSV export of orders and webhooks are not built</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>84.0 to 89.8 and 91.0 to 95.6</t>
+          <t>not applicable</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Partly met</t>
+          <t>Met</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[EXACT CHAPTER ONE WORDING NEEDED] Objective 3, fewer manual entry errors</t>
+          <t>2. To implement an automatic validation engine that checks SKU, quantity, customer details, pricing, duplicate orders, stock and mandatory fields, and to achieve at least 90 percent validation accuracy.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>At least 60 percent fewer manual entry errors</t>
+          <t>At least 90 percent validation accuracy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[DATA PENDING]</t>
+          <t>Primary 87.2 percent, all errors. Secondary 93.6 percent, rule-targeted errors. Replicates 86.8 to 87.2 and 93.0 to 93.6</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[DATA PENDING]</t>
+          <t>84.0 to 89.8 and 91.0 to 95.6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Partly met</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[EXACT CHAPTER ONE WORDING NEEDED] Objective 3, mandatory fields</t>
+          <t>3. To reduce manual data-entry errors by at least 60 percent and to achieve 100 percent completion of mandatory fields.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100 percent mandatory-field completion</t>
+          <t>At least 60 percent fewer manual entry errors</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>258 of 258 orders reaching approval, 100 percent in all three replicates</t>
+          <t>[DATA PENDING]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>98.5 to 100.0</t>
+          <t>[DATA PENDING]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Met</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[EXACT CHAPTER ONE WORDING NEEDED] Objective 4, processing speed</t>
+          <t>3. As above</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>30 to 50 percent faster processing</t>
+          <t>100 percent completion of mandatory fields</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[DATA PENDING]</t>
+          <t>258 of 258 orders reaching approval, 100 percent in all three replicates</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[DATA PENDING]</t>
+          <t>98.5 to 100.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Met</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[EXACT CHAPTER ONE WORDING NEEDED] Objective 5, simulated orders</t>
+          <t>4. To improve order processing speed by 30 to 50 percent through digital approval, payment confirmation, fulfilment and delivery workflows.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>500 simulated orders processed</t>
+          <t>30 to 50 percent faster processing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>500 orders in each of three replicates, 1,500 in all</t>
+          <t>[DATA PENDING]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>not applicable</t>
+          <t>[DATA PENDING]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Met</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Source: Sections 4.2 to 4.4. Accuracy judged on the primary measure with the secondary measure in support.</t>
+          <t>5. To evaluate the usability and acceptance of the system through a questionnaire and a test run of 500 simulated orders.</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Test run of 500 simulated orders</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>500 orders in each of three replicates, 1,500 in all</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>not applicable</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Met</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>5. As above</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Usability and acceptance by questionnaire</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Reported in the questionnaire results, not in this technical chapter</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>not applicable</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Reported separately</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Source: Section 1.3 and Sections 4.2 to 4.4 of this chapter. Accuracy judged on the primary measure with the secondary measure in support.</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3624,6 +3678,11 @@
           <t>Check in Table 2.1</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Data quality dimension in Table 2.1</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3646,6 +3705,11 @@
           <t>Mandatory fields</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Completeness</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3668,6 +3732,11 @@
           <t>SKU</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3690,6 +3759,11 @@
           <t>Quantity</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3712,6 +3786,11 @@
           <t>Stock</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3734,6 +3813,11 @@
           <t>Customer details</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Completeness</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3756,6 +3840,11 @@
           <t>Pricing</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Accuracy and consistency</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3778,6 +3867,11 @@
           <t>Customer details</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Completeness</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3800,6 +3894,11 @@
           <t>Duplicate orders</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Uniqueness</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3819,7 +3918,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>(none; additional check)</t>
+          <t>None, an additional check</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>

--- a/docs/chapter4_final/08_chapter/chapter_tables.xlsx
+++ b/docs/chapter4_final/08_chapter/chapter_tables.xlsx
@@ -3026,13 +3026,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table 4.17: Fictional customer companies used in the simulation</t>
+          <t>Table 4.17: Customer profiles used in the simulation</t>
         </is>
       </c>
     </row>
@@ -3049,15 +3049,10 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>E-mail</t>
+          <t>Region</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
-        <is>
-          <t>Region</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
@@ -3076,15 +3071,10 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>folake.adeyemi@adeyemi1.example</t>
+          <t>Ikeja</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
-        <is>
-          <t>Ikeja</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -3103,15 +3093,10 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>yusuf.adebanjo@agege13.example</t>
+          <t>Ikeja</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
-        <is>
-          <t>Ikeja</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -3130,15 +3115,10 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>blessing.okoro@ajah14.example</t>
+          <t>Lekki-Ajah</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
-        <is>
-          <t>Lekki-Ajah</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -3157,15 +3137,10 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>garba.usman@apapa20.example</t>
+          <t>Lagos Mainland</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
-        <is>
-          <t>Lagos Mainland</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -3184,15 +3159,10 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>segun.olatunji@bodija16.example</t>
+          <t>Ibadan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
-        <is>
-          <t>Ibadan</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
         <is>
           <t>42</t>
         </is>
@@ -3211,15 +3181,10 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>tolulope.ogunleye@eko6.example</t>
+          <t>Lagos Island</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
-        <is>
-          <t>Lagos Island</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
         <is>
           <t>36</t>
         </is>
@@ -3238,15 +3203,10 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ngozi.eze@greenfield7.example</t>
+          <t>Lekki-Ajah</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
-        <is>
-          <t>Lekki-Ajah</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -3265,15 +3225,10 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fatima.sani@gwarinpa15.example</t>
+          <t>Abuja</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>Abuja</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -3292,15 +3247,10 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>oluwaseun.afolabi@ibadan3.example</t>
+          <t>Ibadan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
-        <is>
-          <t>Ibadan</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
         <is>
           <t>31</t>
         </is>
@@ -3319,15 +3269,10 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>chukwuemeka.kanu@kanu2.example</t>
+          <t>Lagos Mainland</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
-        <is>
-          <t>Lagos Mainland</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -3346,15 +3291,10 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>amina.bello@lekki4.example</t>
+          <t>Lekki-Ajah</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
-        <is>
-          <t>Lekki-Ajah</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
         <is>
           <t>28</t>
         </is>
@@ -3373,15 +3313,10 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>funmilayo.adeleke@magodo19.example</t>
+          <t>Ikeja</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
-        <is>
-          <t>Ikeja</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -3400,15 +3335,10 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>kemi.lawson@marina11.example</t>
+          <t>Lagos Island</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
-        <is>
-          <t>Lagos Island</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
         <is>
           <t>17</t>
         </is>
@@ -3427,15 +3357,10 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ibrahim.musa@northgate5.example</t>
+          <t>Abuja</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
-        <is>
-          <t>Abuja</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -3454,15 +3379,10 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>babatunde.oladipo@olaade8.example</t>
+          <t>Ikeja</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
-        <is>
-          <t>Ikeja</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -3481,15 +3401,10 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>adewale.akinyemi@oyo10.example</t>
+          <t>Ibadan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
-        <is>
-          <t>Ibadan</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
         <is>
           <t>22</t>
         </is>
@@ -3508,15 +3423,10 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>uche.nwosu@surulere12.example</t>
+          <t>Lagos Mainland</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
-        <is>
-          <t>Lagos Mainland</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -3535,15 +3445,10 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>chiamaka.obi@victoria17.example</t>
+          <t>Lagos Island</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
-        <is>
-          <t>Lagos Island</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -3562,15 +3467,10 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>emeka.okafor@yaba18.example</t>
+          <t>Lagos Mainland</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
-        <is>
-          <t>Lagos Mainland</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
         <is>
           <t>28</t>
         </is>
@@ -3589,15 +3489,10 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>hauwa.abdullahi@zuma9.example</t>
+          <t>Abuja</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
-        <is>
-          <t>Abuja</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -3606,7 +3501,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Source: replicate 1, database run 5, 03_simulation/replicate1_orders.csv. All names and contact details are fictional.</t>
+          <t>Source: test customer profiles, replicate 1, database run 5, 03_simulation/replicate1_orders.csv.</t>
         </is>
       </c>
     </row>

--- a/docs/chapter4_final/08_chapter/chapter_tables.xlsx
+++ b/docs/chapter4_final/08_chapter/chapter_tables.xlsx
@@ -35,6 +35,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 4.26" sheetId="26" state="visible" r:id="rId26"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 4.27" sheetId="27" state="visible" r:id="rId27"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 4.28" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 4.29" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2726,292 +2727,763 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table 4.16: Planted error types and how each was created</t>
+          <t>Table 4.16: Manual end-to-end test of two orders on 30 October 2026</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Planted error</t>
+          <t>Order</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>How it was planted</t>
+          <t>Step</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Rule expected to catch it</t>
+          <t>Done by</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Time after start, min:s</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Note recorded</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SKU not in catalogue</t>
+          <t>ORD-9371</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>An extra upload line with an unknown code such as XX-417</t>
+          <t>Order started by the customer</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SKU</t>
-        </is>
-      </c>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Discontinued product</t>
+          <t>ORD-9371</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sharp sand added after it was marked inactive for the run</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SKU</t>
-        </is>
-      </c>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1:46</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Missing delivery address</t>
+          <t>ORD-9371</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>No address chosen</t>
+          <t>Passed validation, waiting for Ops Desk</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mandatory fields</t>
-        </is>
-      </c>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1:46</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Missing delivery date</t>
+          <t>ORD-9371</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>No date chosen</t>
+          <t>Approved, invoice issued</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mandatory fields</t>
+          <t>Ops Desk</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2:35</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Good to go</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Delivery date in the past</t>
+          <t>ORD-9371</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Date 1 to 5 days before the run date</t>
+          <t>Payment proof uploaded</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Delivery date and address</t>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3:13</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Proof uploaded (attempt 1)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Quantity below minimum</t>
+          <t>ORD-9371</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Minimum order quantity less one</t>
+          <t>Payment confirmed</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Quantity limits</t>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3:37</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Payment confirmed by Finance</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Quantity above maximum</t>
+          <t>ORD-9371</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Maximum order quantity plus 1 to 50</t>
+          <t>Picking started</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Quantity limits</t>
-        </is>
-      </c>
+          <t>Warehouse</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>3:53</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fractional quantity</t>
+          <t>ORD-9371</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Minimum order quantity plus 0.5</t>
+          <t>Packed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Quantity limits</t>
-        </is>
-      </c>
+          <t>Warehouse</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Quantity above available stock</t>
+          <t>ORD-9371</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Available stock plus one, within the order limits</t>
+          <t>Driver assigned</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Stock availability</t>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>5:01</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Assigned to driver</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Duplicate order</t>
+          <t>ORD-9371</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Same items as the latest clean order that reached approval, else as an earlier history order</t>
+          <t>Picked up by driver</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Duplicate order</t>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>5:48</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Driver confirmed pickup</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Customer account not active</t>
+          <t>ORD-9371</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Draft saved while active, account put on hold or blocked before submission</t>
+          <t>Delivered with the customer code</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Customer status</t>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>6:17</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Delivery code accepted</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Price changed after saving</t>
+          <t>ORD-9370</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>List price of one line raised by 5 percent between saving and submitting</t>
+          <t>Order started by the customer</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pricing</t>
-        </is>
-      </c>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Wrong but valid product</t>
+          <t>ORD-9370</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>A neighbouring product such as 16 mm rods for 12 mm, within all limits</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>7:10</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Plausible quantity typing slip</t>
+          <t>ORD-9370</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cement or iron rods entered at ten times the intended quantity</t>
+          <t>Blocked by validation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>7:10</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Blocking rule failed</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Wrong saved address</t>
+          <t>ORD-9370</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The other of the two saved addresses chosen</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>8:15</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Source: run_simulation_final, supabase/migrations/0007_simulation_final.sql.</t>
+          <t>ORD-9370</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Passed validation, waiting for Ops Desk</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>8:15</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ORD-9370</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Approved, invoice issued</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ops Desk</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>8:37</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Approved by Ops Desk</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ORD-9370</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Payment proof uploaded</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>9:09</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Proof uploaded (attempt 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ORD-9370</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Payment confirmed</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>9:47</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Payment confirmed by Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ORD-9370</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Picking started</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ORD-9370</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Shortage found</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Less stock found than ordered</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ORD-9370</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Packed</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Partial delivery accepted</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ORD-9370</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Driver assigned</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Assigned to driver</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ORD-9370</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Picked up by driver</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Driver confirmed pickup</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ORD-9370</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Delivery failed</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Vehicle breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ORD-9370</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Driver assigned</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Assigned to driver</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ORD-9370</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Picked up by driver</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Driver confirmed pickup</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ORD-9370</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Delivered with the customer code</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Delivery code accepted</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Source: status history of orders ORD-9371 and ORD-9370 in the live database, 02_functional_tests/manual_walkthrough_2026-10-30.json and manual_walkthrough.sql.</t>
         </is>
       </c>
     </row>
@@ -3026,482 +3498,292 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table 4.17: Customer profiles used in the simulation</t>
+          <t>Table 4.17: Planted error types and how each was created</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>Planted error</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Contact person</t>
+          <t>How it was planted</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Region</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Orders</t>
+          <t>Rule expected to catch it</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Adeyemi &amp; Sons Construction Ltd</t>
+          <t>SKU not in catalogue</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Folake Adeyemi</t>
+          <t>An extra upload line with an unknown code such as XX-417</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ikeja</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>26</t>
+          <t>SKU</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Agege Steel Works</t>
+          <t>Discontinued product</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Yusuf Adebanjo</t>
+          <t>Sharp sand added after it was marked inactive for the run</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ikeja</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>19</t>
+          <t>SKU</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ajah Sunrise Housing Co-op</t>
+          <t>Missing delivery address</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Blessing Okoro</t>
+          <t>No address chosen</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lekki-Ajah</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>25</t>
+          <t>Mandatory fields</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Apapa Port Works Supplies</t>
+          <t>Missing delivery date</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Garba Usman</t>
+          <t>No date chosen</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lagos Mainland</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>26</t>
+          <t>Mandatory fields</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bodija Interiors</t>
+          <t>Delivery date in the past</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Segun Olatunji</t>
+          <t>Date 1 to 5 days before the run date</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ibadan</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>42</t>
+          <t>Delivery date and address</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Eko Bridge Contractors</t>
+          <t>Quantity below minimum</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tolulope Ogunleye</t>
+          <t>Minimum order quantity less one</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lagos Island</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>36</t>
+          <t>Quantity limits</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Greenfield Estates Nigeria</t>
+          <t>Quantity above maximum</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ngozi Eze</t>
+          <t>Maximum order quantity plus 1 to 50</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lekki-Ajah</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>23</t>
+          <t>Quantity limits</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Gwarinpa Homes Ltd</t>
+          <t>Fractional quantity</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fatima Sani</t>
+          <t>Minimum order quantity plus 0.5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Abuja</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>19</t>
+          <t>Quantity limits</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ibadan Prime Homes Ltd</t>
+          <t>Quantity above available stock</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Oluwaseun Afolabi</t>
+          <t>Available stock plus one, within the order limits</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ibadan</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>31</t>
+          <t>Stock availability</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kanu Brothers Building Supplies</t>
+          <t>Duplicate order</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Chukwuemeka Kanu</t>
+          <t>Same items as the latest clean order that reached approval, else as an earlier history order</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lagos Mainland</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>Duplicate order</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Lekki Coastal Developers</t>
+          <t>Customer account not active</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Amina Bello</t>
+          <t>Draft saved while active, account put on hold or blocked before submission</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lekki-Ajah</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>28</t>
+          <t>Customer status</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Magodo Residential Ltd</t>
+          <t>Price changed after saving</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Funmilayo Adeleke</t>
+          <t>List price of one line raised by 5 percent between saving and submitting</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ikeja</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>19</t>
+          <t>Pricing</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marina Point Facilities</t>
+          <t>Wrong but valid product</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kemi Lawson</t>
+          <t>A neighbouring product such as 16 mm rods for 12 mm, within all limits</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lagos Island</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Northgate Realty Abuja</t>
+          <t>Plausible quantity typing slip</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ibrahim Musa</t>
+          <t>Cement or iron rods entered at ten times the intended quantity</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Abuja</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>16</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ola-Ade Hardware &amp; Tiles</t>
+          <t>Wrong saved address</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Babatunde Oladipo</t>
+          <t>The other of the two saved addresses chosen</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ikeja</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>21</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Oyo Central Builders</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Adewale Akinyemi</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ibadan</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Surulere Paint &amp; Finish</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Uche Nwosu</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Lagos Mainland</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Victoria Island Fit-Out Ltd</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Chiamaka Obi</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Lagos Island</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Yaba Tech Hub Builders</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Emeka Okafor</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Lagos Mainland</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Zuma Rock Engineering</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Hauwa Abdullahi</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Abuja</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Source: test customer profiles, replicate 1, database run 5, 03_simulation/replicate1_orders.csv.</t>
+          <t>Source: run_simulation_final, supabase/migrations/0007_simulation_final.sql.</t>
         </is>
       </c>
     </row>
@@ -3516,164 +3798,482 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table 4.18: Description of the replicate 1 dataset</t>
+          <t>Table 4.18: Customer profiles used in the simulation</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Measure</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Contact person</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Orders</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Orders</t>
+          <t>Adeyemi &amp; Sons Construction Ltd</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>Folake Adeyemi</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ikeja</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Clean, rule-targeted and no-rule orders</t>
+          <t>Agege Steel Works</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>200, 240, 60</t>
+          <t>Yusuf Adebanjo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ikeja</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Ajah Sunrise Housing Co-op</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>Blessing Okoro</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Lekki-Ajah</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Orders per customer</t>
+          <t>Apapa Port Works Supplies</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16 to 42</t>
+          <t>Garba Usman</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Lagos Mainland</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mean lines per order</t>
+          <t>Bodija Interiors</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>Segun Olatunji</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ibadan</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mean units per order</t>
+          <t>Eko Bridge Contractors</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>Tolulope Ogunleye</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Lagos Island</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>36</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Order value, mean</t>
+          <t>Greenfield Estates Nigeria</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₦1,594,495.04</t>
+          <t>Ngozi Eze</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Lekki-Ajah</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Order value, median</t>
+          <t>Gwarinpa Homes Ltd</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₦981,367.50</t>
+          <t>Fatima Sani</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Order value, range</t>
+          <t>Ibadan Prime Homes Ltd</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₦8,815.00 to ₦20,725,462.50</t>
+          <t>Oluwaseun Afolabi</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ibadan</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total order value</t>
+          <t>Kanu Brothers Building Supplies</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₦797,247,520.00</t>
+          <t>Chukwuemeka Kanu</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Lagos Mainland</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Orders by region</t>
+          <t>Lekki Coastal Developers</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lagos Mainland 102; Ibadan 93; Ikeja 80; Lagos Island 76; Lekki-Ajah 74; Abuja 55; No address given 20</t>
+          <t>Amina Bello</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Lekki-Ajah</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Source: replicate 1, database run 5, 07_analysis/metrics_final.json dataset.</t>
+          <t>Magodo Residential Ltd</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Funmilayo Adeleke</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ikeja</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Marina Point Facilities</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kemi Lawson</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Lagos Island</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Northgate Realty Abuja</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ibrahim Musa</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ola-Ade Hardware &amp; Tiles</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Babatunde Oladipo</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ikeja</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Oyo Central Builders</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Adewale Akinyemi</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ibadan</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Surulere Paint &amp; Finish</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Uche Nwosu</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Lagos Mainland</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Victoria Island Fit-Out Ltd</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Chiamaka Obi</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Lagos Island</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Yaba Tech Hub Builders</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Emeka Okafor</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Lagos Mainland</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Zuma Rock Engineering</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Hauwa Abdullahi</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Source: test customer profiles, replicate 1, database run 5, 03_simulation/replicate1_orders.csv.</t>
         </is>
       </c>
     </row>
@@ -3688,564 +4288,164 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table 4.19: Sample of simulated orders and the decision taken, replicate 1</t>
+          <t>Table 4.19: Description of the replicate 1 dataset</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Order</t>
+          <t>Measure</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Planted error</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Decision</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>First message shown</t>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ORD-3788</t>
+          <t>Orders</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bodija Interiors</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>₦418,175.00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Clean order (no error)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>none</t>
+          <t>500</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ORD-3800</t>
+          <t>Clean, rule-targeted and no-rule orders</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Marina Point Facilities</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>₦869,030.00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>SKU not in catalogue</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Row 4: XX-680 - not in the catalogue</t>
+          <t>200, 240, 60</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ORD-3784</t>
+          <t>Customers</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Marina Point Facilities</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>₦1,656,575.00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Discontinued product</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>SAND-T is no longer sold. Remove it.</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ORD-3782</t>
+          <t>Orders per customer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bodija Interiors</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>₦559,000.00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Missing delivery address</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Choose a delivery address.</t>
+          <t>16 to 42</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ORD-3783</t>
+          <t>Mean lines per order</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gwarinpa Homes Ltd</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>₦1,078,225.00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Missing delivery date</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Choose a delivery date.</t>
+          <t>2.31</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ORD-3789</t>
+          <t>Mean units per order</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Marina Point Facilities</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>₦522,665.00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Delivery date in the past</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>The delivery date is in the past.</t>
+          <t>126.5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ORD-3805</t>
+          <t>Order value, mean</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Magodo Residential Ltd</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>₦621,995.00</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Quantity below minimum</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>PVC pipe, 2 inch, 6 m: quantity must be between 2 and 500.</t>
+          <t>₦1,594,495.04</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ORD-3793</t>
+          <t>Order value, median</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lekki Coastal Developers</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>₦15,103,642.50</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Quantity above maximum</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Aluminium roofing sheet, 0.55 mm: quantity must be between 10 and 1000.</t>
+          <t>₦981,367.50</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ORD-3785</t>
+          <t>Order value, range</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Victoria Island Fit-Out Ltd</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>₦732,075.00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Fractional quantity</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>PVC-4 - Quantity must be a whole number</t>
+          <t>₦8,815.00 to ₦20,725,462.50</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ORD-3786</t>
+          <t>Total order value</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bodija Interiors</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>₦6,077,405.00</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Quantity above available stock</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Iron rod, 12 mm: not enough stock for this quantity. Reduce it.</t>
+          <t>₦797,247,520.00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORD-3838</t>
+          <t>Orders by region</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Victoria Island Fit-Out Ltd</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>₦764,970.00</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Duplicate order</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Warned</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Iron rod, 12 mm: 97 is far above this customer's usual 29.</t>
+          <t>Lagos Mainland 102; Ibadan 93; Ikeja 80; Lagos Island 76; Lekki-Ajah 74; Abuja 55; No address given 20</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ORD-3798</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Gwarinpa Homes Ltd</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>₦24,940.00</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Customer account not active</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>The customer account is not active.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>ORD-3802</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Oyo Central Builders</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>₦234,350.00</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Price changed after the order was saved</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Cement, 50 kg bag: price changed from 9500.00 to 10000.00. Save the order again to update it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>ORD-3806</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Gwarinpa Homes Ltd</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>₦1,030,925.00</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Wrong but valid product</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>ORD-3792</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Ajah Sunrise Housing Co-op</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>₦3,445,805.00</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Plausible quantity typing slip</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Warned</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Cement, 50 kg bag: 190 is far above this customer's usual 23.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ORD-3812</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Ola-Ade Hardware &amp; Tiles</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>₦859,677.50</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Wrong saved address</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Source: replicate 1, database run 5, first order of each kind in 03_simulation/replicate1_orders.csv.</t>
+          <t>Source: replicate 1, database run 5, 07_analysis/metrics_final.json dataset.</t>
         </is>
       </c>
     </row>
@@ -5104,550 +5304,558 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table 4.20: Detection by planted error type, replicate 1</t>
+          <t>Table 4.20: Sample of simulated orders and the decision taken, replicate 1</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Order</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>Planted error</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Has rule</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Flagged</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Detection %</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>95% CI</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Caught by expected rule</t>
+          <t>First message shown</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>ORD-3788</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bodija Interiors</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>₦418,175.00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>Clean order (no error)</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>28 flagged</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>14.0 false alarms</t>
-        </is>
-      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9.9 to 19.5</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>ORD-3800</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Marina Point Facilities</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>₦869,030.00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>SKU not in catalogue</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>20/20</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>83.9 to 100.0</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>Row 4: XX-680 - not in the catalogue</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>ORD-3784</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Marina Point Facilities</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>₦1,656,575.00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>Discontinued product</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>20/20</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>83.9 to 100.0</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>SAND-T is no longer sold. Remove it.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>ORD-3782</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Bodija Interiors</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>₦559,000.00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>Missing delivery address</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>20/20</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>83.9 to 100.0</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>Choose a delivery address.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>ORD-3783</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Gwarinpa Homes Ltd</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>₦1,078,225.00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>Missing delivery date</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>20/20</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>83.9 to 100.0</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>Choose a delivery date.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>ORD-3789</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Marina Point Facilities</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>₦522,665.00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>Delivery date in the past</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>20/20</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>83.9 to 100.0</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>The delivery date is in the past.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>ORD-3805</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Magodo Residential Ltd</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>₦621,995.00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>Quantity below minimum</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>20/20</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>83.9 to 100.0</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>PVC pipe, 2 inch, 6 m: quantity must be between 2 and 500.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>ORD-3793</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Lekki Coastal Developers</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>₦15,103,642.50</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>Quantity above maximum</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>20/20</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>83.9 to 100.0</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>Aluminium roofing sheet, 0.55 mm: quantity must be between 10 and 1000.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>ORD-3785</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Victoria Island Fit-Out Ltd</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>₦732,075.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>Fractional quantity</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>20/20</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>83.9 to 100.0</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>PVC-4 - Quantity must be a whole number</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>ORD-3786</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Bodija Interiors</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>₦6,077,405.00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>Quantity above available stock</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>20/20</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>83.9 to 100.0</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>Iron rod, 12 mm: not enough stock for this quantity. Reduce it.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>ORD-3838</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Victoria Island Fit-Out Ltd</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>₦764,970.00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>Duplicate order</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>20/20</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>83.9 to 100.0</t>
+          <t>Warned</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>Iron rod, 12 mm: 97 is far above this customer's usual 29.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>ORD-3798</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Gwarinpa Homes Ltd</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>₦24,940.00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>Customer account not active</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>20/20</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>83.9 to 100.0</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>The customer account is not active.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>ORD-3802</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Oyo Central Builders</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>₦234,350.00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>Price changed after the order was saved</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>20/20</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>83.9 to 100.0</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>Cement, 50 kg bag: price changed from 9500.00 to 10000.00. Save the order again to update it.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>ORD-3806</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Gwarinpa Homes Ltd</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>₦1,030,925.00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>Wrong but valid product</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>5/20</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11.2 to 46.9</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>5 by other rules</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>ORD-3792</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ajah Sunrise Housing Co-op</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>₦3,445,805.00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>Plausible quantity typing slip</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>14/20</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>48.1 to 85.5</t>
+          <t>Warned</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>14 by other rules</t>
+          <t>Cement, 50 kg bag: 190 is far above this customer's usual 23.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>ORD-3812</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ola-Ade Hardware &amp; Tiles</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>₦859,677.50</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>Wrong saved address</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>5/20</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11.2 to 46.9</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>5 by other rules</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Source: replicate 1, 07_analysis/metrics_final.json by_type, workbook sheet R1 Summary section D.</t>
+          <t>Source: replicate 1, database run 5, first order of each kind in 03_simulation/replicate1_orders.csv.</t>
         </is>
       </c>
     </row>
@@ -5662,139 +5870,556 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table 4.21: Definitions of the classification measures</t>
+          <t>Table 4.21: Detection by planted error type, replicate 1</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Measure</t>
+          <t>Planted error</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Has rule</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Formula</t>
+          <t>Flagged</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Detection %</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>95% CI</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Caught by expected rule</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Accuracy</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Share of all orders the system judged correctly, erroneous orders flagged and clean orders passed</t>
-        </is>
-      </c>
+          <t>Clean order (no error)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>(TP + TN) / all orders</t>
-        </is>
-      </c>
+          <t>28 flagged</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>14.0 false alarms</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>9.9 to 19.5</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Precision</t>
+          <t>SKU not in catalogue</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Of the orders flagged, the share that really carried an error</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TP / (TP + FP)</t>
+          <t>20/20</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>83.9 to 100.0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Discontinued product</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Of the orders that carried an error, the share the system flagged</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TP / (TP + FN)</t>
+          <t>20/20</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>83.9 to 100.0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Specificity</t>
+          <t>Missing delivery address</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Of the clean orders, the share passed without a flag</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TN / (TN + FP)</t>
+          <t>20/20</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>83.9 to 100.0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>False-alarm rate</t>
+          <t>Missing delivery date</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Of the clean orders, the share flagged</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FP / (FP + TN)</t>
+          <t>20/20</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>83.9 to 100.0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F1 score</t>
+          <t>Delivery date in the past</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Harmonic mean of precision and recall</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2 x P x R / (P + R)</t>
+          <t>20/20</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>83.9 to 100.0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Source: standard definitions. TP true positive, FN false negative, FP false positive, TN true negative.</t>
+          <t>Quantity below minimum</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>20/20</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>83.9 to 100.0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Quantity above maximum</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>20/20</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>83.9 to 100.0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Fractional quantity</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>20/20</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>83.9 to 100.0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Quantity above available stock</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>20/20</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>83.9 to 100.0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Duplicate order</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>20/20</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>83.9 to 100.0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Customer account not active</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>20/20</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>83.9 to 100.0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Price changed after the order was saved</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>20/20</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>83.9 to 100.0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Wrong but valid product</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>5/20</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>11.2 to 46.9</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>5 by other rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Plausible quantity typing slip</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>14/20</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>48.1 to 85.5</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>14 by other rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Wrong saved address</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>5/20</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>11.2 to 46.9</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>5 by other rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Source: replicate 1, 07_analysis/metrics_final.json by_type, workbook sheet R1 Summary section D.</t>
         </is>
       </c>
     </row>
@@ -5809,116 +6434,139 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table 4.22: Confusion matrices, replicate 1</t>
+          <t>Table 4.22: Definitions of the classification measures</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Measure set</t>
+          <t>Measure</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Error flagged</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Error passed</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Clean flagged</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Clean passed</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Orders</t>
+          <t>Formula</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Primary, all errors</t>
+          <t>Accuracy</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>Share of all orders the system judged correctly, erroneous orders flagged and clean orders passed</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>500</t>
+          <t>(TP + TN) / all orders</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Secondary, rule-targeted errors</t>
+          <t>Precision</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>Of the orders flagged, the share that really carried an error</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>440</t>
+          <t>TP / (TP + FP)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Source: replicate 1, 07_analysis/metrics_final.json confusion_all_errors and confusion_rule_targeted, workbook R1 Summary sections B and C.</t>
+          <t>Recall</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Of the orders that carried an error, the share the system flagged</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TP / (TP + FN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Specificity</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Of the clean orders, the share passed without a flag</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TN / (TN + FP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>False-alarm rate</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Of the clean orders, the share flagged</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>FP / (FP + TN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F1 score</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Harmonic mean of precision and recall</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2 x P x R / (P + R)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Source: standard definitions. TP true positive, FN false negative, FP false positive, TN true negative.</t>
         </is>
       </c>
     </row>
@@ -5933,209 +6581,116 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table 4.23: Validation measures with 95 percent Wilson intervals, replicate 1</t>
+          <t>Table 4.23: Confusion matrices, replicate 1</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Measure</t>
+          <t>Measure set</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Primary %</t>
+          <t>Error flagged</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Primary 95% CI</t>
+          <t>Error passed</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Secondary %</t>
+          <t>Clean flagged</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Secondary 95% CI</t>
+          <t>Clean passed</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Orders</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>Primary, all errors</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>264</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>84.0 to 89.8</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>28</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>91.0 to 95.6</t>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>500</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Precision</t>
+          <t>Secondary, rule-targeted errors</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>240</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>86.5 to 93.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>28</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>85.3 to 92.7</t>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>440</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Recall</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>83.8 to 91.2</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>98.4 to 100.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Specificity</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>86.0</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>80.5 to 90.1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>86.0</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>80.5 to 90.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>False-alarm rate</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>9.9 to 19.5</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>9.9 to 19.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>F1 score</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>not a single proportion</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>94.5</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>not a single proportion</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Source: replicate 1, 07_analysis/metrics_final.json, workbook R1 Summary sections B and C.</t>
+          <t>Source: replicate 1, 07_analysis/metrics_final.json confusion_all_errors and confusion_rule_targeted, workbook R1 Summary sections B and C.</t>
         </is>
       </c>
     </row>
@@ -6150,390 +6705,209 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table 4.24: Rule activity and false alarms, replicate 1</t>
+          <t>Table 4.24: Validation measures with 95 percent Wilson intervals, replicate 1</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Rule</t>
+          <t>Measure</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Severity</t>
+          <t>Primary %</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Orders fired</t>
+          <t>Primary 95% CI</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>On its target type</t>
+          <t>Secondary %</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>On other error types</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>On clean orders</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>False alarms per clean order, 95% CI</t>
+          <t>Secondary 95% CI</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mandatory fields</t>
+          <t>Accuracy</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Blocking</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>84.0 to 89.8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0.0 (0.0 to 1.9)</t>
+          <t>91.0 to 95.6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SKU and product active</t>
+          <t>Precision</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Blocking</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>86.5 to 93.3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0.0 (0.0 to 1.9)</t>
+          <t>85.3 to 92.7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Quantity limits</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Blocking</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>83.8 to 91.2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0.0 (0.0 to 1.9)</t>
+          <t>98.4 to 100.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Stock availability</t>
+          <t>Specificity</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Blocking</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>80.5 to 90.1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0.0 (0.0 to 1.9)</t>
+          <t>80.5 to 90.1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Customer status</t>
+          <t>False-alarm rate</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Blocking</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>9.9 to 19.5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0.0 (0.0 to 1.9)</t>
+          <t>9.9 to 19.5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pricing</t>
+          <t>F1 score</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Blocking</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>not a single proportion</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0.0 (0.0 to 1.9)</t>
+          <t>not a single proportion</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Delivery date and address</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Blocking</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0.0 (0.0 to 1.9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Duplicate order</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0.5 (0.1 to 2.8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Unusual quantity</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>13.5 (9.4 to 18.9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Source: replicate 1, 07_analysis/metrics_final.json rules, workbook R1 Summary section E.</t>
+          <t>Source: replicate 1, 07_analysis/metrics_final.json, workbook R1 Summary sections B and C.</t>
         </is>
       </c>
     </row>
@@ -6548,236 +6922,390 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table 4.25: Validation time per order in milliseconds, replicate 1</t>
+          <t>Table 4.25: Rule activity and false alarms, replicate 1</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Statistic</t>
+          <t>Rule</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>All orders</t>
+          <t>Severity</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Orders fired</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Warned</t>
+          <t>On its target type</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>On other error types</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>On clean orders</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>False alarms per clean order, 95% CI</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Orders</t>
+          <t>Mandatory fields</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>Blocking</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.0 (0.0 to 1.9)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mean</t>
+          <t>SKU and product active</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>28.72</t>
+          <t>Blocking</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>27.85</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.0 (0.0 to 1.9)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SD, sample</t>
+          <t>Quantity limits</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23.27</t>
+          <t>Blocking</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21.34</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>25.28</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>24.33</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.0 (0.0 to 1.9)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Median</t>
+          <t>Stock availability</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>Blocking</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>22.31</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>22.59</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21.56</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.0 (0.0 to 1.9)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>95th percentile</t>
+          <t>Customer status</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>74.72</t>
+          <t>Blocking</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>71.59</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>80.19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>75.57</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.0 (0.0 to 1.9)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Minimum</t>
+          <t>Pricing</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>Blocking</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.0 (0.0 to 1.9)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Maximum</t>
+          <t>Delivery date and address</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>124.31</t>
+          <t>Blocking</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>94.84</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>114.3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>124.31</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.0 (0.0 to 1.9)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Source: replicate 1, 07_analysis/metrics_final.json validation_ms, workbook R1 Summary section F.</t>
+          <t>Duplicate order</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.5 (0.1 to 2.8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Unusual quantity</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>13.5 (9.4 to 18.9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Source: replicate 1, 07_analysis/metrics_final.json rules, workbook R1 Summary section E.</t>
         </is>
       </c>
     </row>
@@ -6792,452 +7320,236 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table 4.26: Key measures in each replicate</t>
+          <t>Table 4.26: Validation time per order in milliseconds, replicate 1</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Measure</t>
+          <t>Statistic</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Replicate 1</t>
+          <t>All orders</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Replicate 2</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Replicate 3</t>
+          <t>Warned</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Accuracy, all errors</t>
+          <t>Orders</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>500</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>208</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>72</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>86.8 to 87.2</t>
+          <t>220</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Precision, all errors</t>
+          <t>Mean</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>28.72</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>27.85</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>31.84</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>89.5 to 90.4</t>
+          <t>28.53</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Recall, all errors</t>
+          <t>SD, sample</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>23.27</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>21.34</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>25.28</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>88.0 to 88.3</t>
+          <t>24.33</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Specificity</t>
+          <t>Median</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>22.16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>22.31</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>22.59</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>84.5 to 86.0</t>
+          <t>21.56</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>False-alarm rate</t>
+          <t>95th percentile</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>74.72</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>71.59</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>80.19</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14.0 to 15.5</t>
+          <t>75.57</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F1, all errors</t>
+          <t>Minimum</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>88.9 to 89.2</t>
+          <t>2.45</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Accuracy, rule-targeted errors</t>
+          <t>Maximum</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>124.31</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>94.84</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>114.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>93.0 to 93.6</t>
+          <t>124.31</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Precision, rule-targeted errors</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>89.6</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>88.6</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>88.6 to 89.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Recall, rule-targeted errors</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>100.0 to 100.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>F1, rule-targeted errors</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>94.5</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>93.9</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>94.3</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>93.9 to 94.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>No-rule errors flagged</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>41.7</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>41.7</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>40.0 to 41.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Mean validation time, ms</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>28.72</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>29.84</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2.33</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2.33 to 29.84</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Median validation time, ms</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>22.16</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>22.88</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>2.34 to 22.88</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>95th percentile validation time, ms</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>74.72</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>78.92</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2.84</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>2.84 to 78.92</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Mandatory-field completion, orders reaching approval</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>100.0 to 100.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Source: 07_analysis/metrics_final.json replicate_range, workbook sheet Replicate range.</t>
+          <t>Source: replicate 1, 07_analysis/metrics_final.json validation_ms, workbook R1 Summary section F.</t>
         </is>
       </c>
     </row>
@@ -7252,349 +7564,452 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table 4.27: Unusual-quantity sensitivity on replicate 1</t>
+          <t>Table 4.27: Key measures in each replicate</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Threshold</t>
+          <t>Measure</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Earlier orders</t>
+          <t>Replicate 1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Clean flagged</t>
+          <t>Replicate 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>False-alarm %</t>
+          <t>Replicate 3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>95% CI</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Slips flagged</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Slip detection %</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>95% CI</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Accuracy, all errors %</t>
+          <t>Range</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3 x average</t>
+          <t>Accuracy, all errors</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28/200</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9.9 to 19.5</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>14/20</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>48.1 to 85.5</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>87.2</t>
+          <t>86.8 to 87.2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4 x average</t>
+          <t>Precision, all errors</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20/200</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>6.6 to 14.9</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>12/20</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>38.7 to 78.1</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>88.0</t>
+          <t>89.5 to 90.4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5 x average</t>
+          <t>Recall, all errors</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>17/200</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5.4 to 13.2</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>11/20</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>34.2 to 74.2</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>88.2</t>
+          <t>88.0 to 88.3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3 x average</t>
+          <t>Specificity</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38/200</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>14.2 to 25.0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>16/20</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>58.4 to 91.9</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>85.4</t>
+          <t>84.5 to 86.0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4 x average</t>
+          <t>False-alarm rate</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>23/200</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>7.8 to 16.7</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>14/20</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>48.1 to 85.5</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>88.0</t>
+          <t>14.0 to 15.5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5 x average</t>
+          <t>F1, all errors</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16/200</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5.0 to 12.6</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>12/20</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>38.7 to 78.1</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>88.6</t>
+          <t>88.9 to 89.2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Source: replays of database run 5 as runs 8 to 13, 04_sensitivity/sensitivity_results.csv, workbook sheet Sensitivity.</t>
+          <t>Accuracy, rule-targeted errors</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>93.6</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>93.4</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>93.0 to 93.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Precision, rule-targeted errors</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>89.6</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>88.6</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>88.6 to 89.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Recall, rule-targeted errors</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>100.0 to 100.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F1, rule-targeted errors</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>94.5</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>93.9</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>94.3</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>93.9 to 94.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>No-rule errors flagged</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>41.7</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>41.7</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>40.0 to 41.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Mean validation time, ms</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>28.72</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>29.84</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2.33 to 29.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Median validation time, ms</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>22.16</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>22.88</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2.34 to 22.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>95th percentile validation time, ms</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>74.72</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>78.92</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2.84</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2.84 to 78.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Mandatory-field completion, orders reaching approval</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>100.0 to 100.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Source: 07_analysis/metrics_final.json replicate_range, workbook sheet Replicate range.</t>
         </is>
       </c>
     </row>
@@ -7609,13 +8024,370 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Table 4.28: Unusual-quantity sensitivity on replicate 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Threshold</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Earlier orders</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Clean flagged</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>False-alarm %</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>95% CI</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Slips flagged</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Slip detection %</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>95% CI</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Accuracy, all errors %</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>3 x average</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>28/200</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>9.9 to 19.5</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>14/20</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>48.1 to 85.5</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>87.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>4 x average</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>20/200</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>6.6 to 14.9</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>12/20</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>38.7 to 78.1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>5 x average</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>17/200</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>5.4 to 13.2</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>11/20</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>34.2 to 74.2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>88.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3 x average</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>38/200</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>14.2 to 25.0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>16/20</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>58.4 to 91.9</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>85.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4 x average</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>23/200</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>7.8 to 16.7</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>14/20</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>48.1 to 85.5</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>5 x average</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>16/200</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5.0 to 12.6</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>12/20</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>38.7 to 78.1</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>88.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Source: replays of database run 5 as runs 8 to 13, 04_sensitivity/sensitivity_results.csv, workbook sheet Sensitivity.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table 4.28: Objectives of Section 1.3 and their success criteria</t>
+          <t>Table 4.29: Objectives of Section 1.3 and their success criteria</t>
         </is>
       </c>
     </row>

--- a/docs/chapter4_final/08_chapter/chapter_tables.xlsx
+++ b/docs/chapter4_final/08_chapter/chapter_tables.xlsx
@@ -8485,17 +8485,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[DATA PENDING]</t>
+          <t>Every rule-targeted error was stopped in all three replicates. 40.0 to 41.7 percent of errors with no rule were flagged. Reduction against manual entry not yet measured</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[DATA PENDING]</t>
+          <t>not applicable</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
@@ -8539,17 +8539,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[DATA PENDING]</t>
+          <t>Median validation time 2.34 to 22.88 ms per order across the replicates. Gain against manual handling not yet measured</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[DATA PENDING]</t>
+          <t>not applicable</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>

--- a/docs/chapter4_final/08_chapter/chapter_tables.xlsx
+++ b/docs/chapter4_final/08_chapter/chapter_tables.xlsx
@@ -36,6 +36,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 4.27" sheetId="27" state="visible" r:id="rId27"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 4.28" sheetId="28" state="visible" r:id="rId28"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 4.29" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 4.30" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8387,159 +8388,159 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table 4.29: Objectives of Section 1.3 and their success criteria</t>
+          <t>Table 4.29: Manual entry and Verity on the same 40 orders</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Objective, Chapter One wording</t>
+          <t>Measure</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>Manual entry</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Result</t>
+          <t>95% CI</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Verity</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>95% CI</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Status</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1. To design and develop a web-based order processing system that replaces manual order entry done through Excel sheets and through e-mail and WhatsApp messages.</t>
+          <t>Orders with an error reaching the record</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A working web-based system through which orders are entered and processed without rekeying</t>
+          <t>29 of 40, 72.5 percent</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Built and deployed. Orders are entered in the portal, from an uploaded Excel or CSV sheet, or from a pasted message. 23 of 26 functional tests passed. CSV export of orders and webhooks are not built</t>
+          <t>57.2 to 83.9</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>not applicable</t>
+          <t>6 of 40, 15.0 percent</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Met</t>
+          <t>7.1 to 29.1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2. To implement an automatic validation engine that checks SKU, quantity, customer details, pricing, duplicate orders, stock and mandatory fields, and to achieve at least 90 percent validation accuracy.</t>
+          <t>Planted errors flagged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>At least 90 percent validation accuracy</t>
+          <t>6 of 26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Primary 87.2 percent, all errors. Secondary 93.6 percent, rule-targeted errors. Replicates 86.8 to 87.2 and 93.0 to 93.6</t>
+          <t>11.0 to 42.1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>84.0 to 89.8 and 91.0 to 95.6</t>
+          <t>20 of 26</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Partly met</t>
+          <t>57.9 to 89.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3. To reduce manual data-entry errors by at least 60 percent and to achieve 100 percent completion of mandatory fields.</t>
+          <t>Rule-targeted errors flagged</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>At least 60 percent fewer manual entry errors</t>
+          <t>6 of 19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Every rule-targeted error was stopped in all three replicates. 40.0 to 41.7 percent of errors with no rule were flagged. Reduction against manual entry not yet measured</t>
+          <t>15.4 to 54.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>not applicable</t>
+          <t>19 of 19</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>83.2 to 100.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3. As above</t>
+          <t>Errors with no rule flagged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100 percent completion of mandatory fields</t>
+          <t>0 of 7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>258 of 258 orders reaching approval, 100 percent in all three replicates</t>
+          <t>0.0 to 35.4</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>98.5 to 100.0</t>
+          <t>1 of 7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Met</t>
+          <t>2.6 to 51.3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4. To improve order processing speed by 30 to 50 percent through digital approval, payment confirmation, fulfilment and delivery workflows.</t>
+          <t>Orders with a field typed differently from the message</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30 to 50 percent faster processing</t>
+          <t>19 of 40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Median validation time 2.34 to 22.88 ms per order across the replicates. Gain against manual handling not yet measured</t>
+          <t>32.9 to 62.5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -8547,70 +8548,58 @@
           <t>not applicable</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5. To evaluate the usability and acceptance of the system through a questionnaire and a test run of 500 simulated orders.</t>
+          <t>Clean orders wrongly flagged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Test run of 500 simulated orders</t>
+          <t>0 of 14</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>500 orders in each of three replicates, 1,500 in all</t>
+          <t>0.0 to 21.5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>not applicable</t>
+          <t>1 of 14</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Met</t>
+          <t>1.3 to 31.5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5. As above</t>
+          <t>Time per order, median and mean</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Usability and acceptance shown by the questionnaire</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>System Usability Scale mean 48.86, significantly below 68. 38.5 percent would use Verity</t>
-        </is>
-      </c>
+          <t>180 s and 246 s</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>45.35 to 52.38</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
+          <t>not measured for a person</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Source: Section 1.3 and Sections 4.2 to 4.5 of this chapter. Accuracy judged on the primary measure with the secondary measure in support.</t>
+          <t>Source: Entry sheets of participants P01 and P02, answer key of the comparison pack and replicate 1 of the simulation, scored with score_manual_vs_simulation.py.</t>
         </is>
       </c>
     </row>
@@ -9225,6 +9214,250 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Table 4.30: Objectives of Section 1.3 and their success criteria</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Objective, Chapter One wording</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Criterion</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>95% CI</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1. To design and develop a web-based order processing system that replaces manual order entry done through Excel sheets and through e-mail and WhatsApp messages.</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>A working web-based system through which orders are entered and processed without rekeying</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Built and deployed. Orders are entered in the portal, from an uploaded Excel or CSV sheet, or from a pasted message. 23 of 26 functional tests passed. CSV export of orders and webhooks are not built</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>not applicable</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Met</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2. To implement an automatic validation engine that checks SKU, quantity, customer details, pricing, duplicate orders, stock and mandatory fields, and to achieve at least 90 percent validation accuracy.</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>At least 90 percent validation accuracy</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Primary 87.2 percent, all errors. Secondary 93.6 percent, rule-targeted errors. Replicates 86.8 to 87.2 and 93.0 to 93.6</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>84.0 to 89.8 and 91.0 to 95.6</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Partly met</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3. To reduce manual data-entry errors by at least 60 percent and to achieve 100 percent completion of mandatory fields.</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>At least 60 percent fewer manual entry errors</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>An error reached the record in 29 of 40 orders by hand and 6 of the same 40 through Verity, a reduction of 79.3 percent. Two participants, indicative</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>57.2 to 83.9 and 7.1 to 29.1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Met, indicative</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3. As above</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>100 percent completion of mandatory fields</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>258 of 258 orders reaching approval, 100 percent in all three replicates</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>98.5 to 100.0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Met</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4. To improve order processing speed by 30 to 50 percent through digital approval, payment confirmation, fulfilment and delivery workflows.</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>30 to 50 percent faster processing</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Manual handling took a median of 180 s per order. Verity validates in 2.34 to 22.88 ms, but the time a person spends entering an order in Verity was not measured</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>not applicable</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>5. To evaluate the usability and acceptance of the system through a questionnaire and a test run of 500 simulated orders.</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Test run of 500 simulated orders</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>500 orders in each of three replicates, 1,500 in all</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>not applicable</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Met</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>5. As above</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Usability and acceptance shown by the questionnaire</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>System Usability Scale mean 48.86, significantly below 68. 38.5 percent would use Verity</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>45.35 to 52.38</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Not met</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Source: Section 1.3 and Sections 4.2 to 4.5 of this chapter. Accuracy judged on the primary measure with the secondary measure in support.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
